--- a/Camera_usd_xform_joint_counts.xlsx
+++ b/Camera_usd_xform_joint_counts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="USD审查" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'USD审查'!$A$1:$Q$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'USD审查'!$A$1:$Q$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,10 +443,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -613,8 +613,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -622,7 +630,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>表格不存在</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -692,8 +700,16 @@
           <t>3</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -701,7 +717,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>表格不存在</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -771,8 +787,16 @@
           <t>3</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -780,7 +804,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>表格不存在</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -850,8 +874,16 @@
           <t>5</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -859,7 +891,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>表格不存在</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -929,8 +961,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -938,7 +978,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>表格不存在</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1008,8 +1048,16 @@
           <t>4</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -1017,7 +1065,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>表格不存在</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1087,8 +1135,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -1096,7 +1152,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>表格不存在</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1166,8 +1222,16 @@
           <t>5</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -1175,7 +1239,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>表格不存在</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1245,8 +1309,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -1254,7 +1326,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>表格不存在</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1324,8 +1396,16 @@
           <t>6</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -1333,7 +1413,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>表格不存在</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1403,8 +1483,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -1412,7 +1500,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>表格不存在</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1482,8 +1570,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -1491,7 +1587,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>表格不存在</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1561,8 +1657,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -1570,7 +1674,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>表格不存在</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1640,8 +1744,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -1649,7 +1761,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>表格不存在</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -1719,8 +1831,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -1728,7 +1848,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>表格不存在</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -1798,8 +1918,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -1807,7 +1935,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>表格不存在</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -1877,8 +2005,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -1886,7 +2022,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>表格不存在</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -1956,8 +2092,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -1965,7 +2109,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>表格不存在</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2035,8 +2179,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -2044,7 +2196,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>表格不存在</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2114,8 +2266,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -2123,807 +2283,17 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>表格不存在</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CEH30235081872446-1</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>CEH30235081872446-1.usd</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>CEH30235081872446-1\CEH30235081872446-1.usd</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>root_camera</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>/root_camera</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>/root_camera</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>表格不存在</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CEH30235081872446-2</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>CEH30235081872446-2.usd</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>CEH30235081872446-2\CEH30235081872446-2.usd</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>root_camera</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>/root_camera</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>/root_camera</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>表格不存在</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CEH30235081872446-3</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>CEH30235081872446-3.usd</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>CEH30235081872446-3\CEH30235081872446-3.usd</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>root_camera</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>/root_camera</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>/root_camera</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>表格不存在</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CEH30235081872446-5</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>CEH30235081872446-5.usd</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>CEH30235081872446-5\CEH30235081872446-5.usd</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>root_camera</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>/root_camera</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>/root_camera</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>表格不存在</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CEH30235081872446-6</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>CEH30235081872446-6.usd</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>CEH30235081872446-6\CEH30235081872446-6.usd</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>root_camera</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>/root_camera</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>/root_camera</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>表格不存在</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CEH30235081872446-7</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>CEH30235081872446-7.usd</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>CEH30235081872446-7\CEH30235081872446-7.usd</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>root_camera</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>/root_camera</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>/root_camera</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr"/>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>表格不存在</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CEH30235081872446-8</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>CEH30235081872446-8.usd</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>CEH30235081872446-8\CEH30235081872446-8.usd</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>root_camera</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>/root_camera</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>/root_camera</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>表格不存在</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>errorCDH30235081704773-9</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>CDH30235081704773-9.usd</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>errorCDH30235081704773-9\CDH30235081704773-9.usd</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>root_camera</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>/root_camera</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>/root_camera</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>表格不存在</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>errorCDH30235081704773-11</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>CDH30235081704773-11.usd</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>errorCDH30235081704773-11\CDH30235081704773-11.usd</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>root_camera</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>/root_camera</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>/root_camera</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>表格不存在</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>errorCEH30235081872446-4</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>CEH30235081872446-4.usd</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>errorCEH30235081872446-4\CEH30235081872446-4.usd</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>root_camera</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>/root_camera</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>/root_camera</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>表格不存在</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q31"/>
+  <autoFilter ref="A1:Q21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>